--- a/output/Data and Chart Outputs/china_nbs_clean_energy_products_monthly.xlsx
+++ b/output/Data and Chart Outputs/china_nbs_clean_energy_products_monthly.xlsx
@@ -27,9 +27,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="mmm/yy"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="mmm/yy"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -69,13 +70,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -169,6 +169,7 @@
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -325,11 +326,23 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
         <numFmt formatCode="mmm/yy" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
         <tickLblSkip val="4"/>
@@ -357,14 +370,22 @@
               </a:p>
             </rich>
           </tx>
+          <overlay val="0"/>
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
+      <spPr>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
     </plotArea>
     <legend>
       <legendPos val="b"/>
+      <overlay val="0"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -395,6 +416,7 @@
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <lineChart>
@@ -444,11 +466,23 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
         <numFmt formatCode="mmm/yy" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
         <tickLblSkip val="4"/>
@@ -476,15 +510,19 @@
               </a:p>
             </rich>
           </tx>
+          <overlay val="0"/>
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
+      <spPr>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
     </plotArea>
-    <legend>
-      <legendPos val="b"/>
-    </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
@@ -514,6 +552,7 @@
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <lineChart>
@@ -563,11 +602,23 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
         <numFmt formatCode="mmm/yy" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
         <tickLblSkip val="4"/>
@@ -595,15 +646,19 @@
               </a:p>
             </rich>
           </tx>
+          <overlay val="0"/>
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
+      <spPr>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
     </plotArea>
-    <legend>
-      <legendPos val="b"/>
-    </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
@@ -633,6 +688,7 @@
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <lineChart>
@@ -682,11 +738,23 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
         <numFmt formatCode="mmm/yy" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
         <tickLblSkip val="4"/>
@@ -714,15 +782,19 @@
               </a:p>
             </rich>
           </tx>
+          <overlay val="0"/>
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
+      <spPr>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
     </plotArea>
-    <legend>
-      <legendPos val="b"/>
-    </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
@@ -752,6 +824,7 @@
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <lineChart>
@@ -801,11 +874,23 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
         <numFmt formatCode="mmm/yy" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
         <tickLblSkip val="4"/>
@@ -833,15 +918,19 @@
               </a:p>
             </rich>
           </tx>
+          <overlay val="0"/>
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
+      <spPr>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
     </plotArea>
-    <legend>
-      <legendPos val="b"/>
-    </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
@@ -871,6 +960,7 @@
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <lineChart>
@@ -956,11 +1046,23 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
         <numFmt formatCode="mmm/yy" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
         <tickLblSkip val="4"/>
@@ -988,14 +1090,22 @@
               </a:p>
             </rich>
           </tx>
+          <overlay val="0"/>
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
+      <spPr>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
     </plotArea>
     <legend>
       <legendPos val="b"/>
+      <overlay val="0"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -1026,6 +1136,7 @@
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <lineChart>
@@ -1111,11 +1222,23 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
         <numFmt formatCode="mmm/yy" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
         <tickLblSkip val="4"/>
@@ -1143,14 +1266,22 @@
               </a:p>
             </rich>
           </tx>
+          <overlay val="0"/>
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
+      <spPr>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
     </plotArea>
     <legend>
       <legendPos val="b"/>
+      <overlay val="0"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -1181,6 +1312,7 @@
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <lineChart>
@@ -1230,11 +1362,23 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
         <numFmt formatCode="mmm/yy" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
         <tickLblSkip val="4"/>
@@ -1262,15 +1406,19 @@
               </a:p>
             </rich>
           </tx>
+          <overlay val="0"/>
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
+      <spPr>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
     </plotArea>
-    <legend>
-      <legendPos val="b"/>
-    </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
@@ -1815,6 +1963,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
@@ -1829,6 +1978,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
@@ -1843,6 +1993,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
@@ -1857,6 +2008,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
@@ -5370,7 +5522,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>44256</v>
       </c>
       <c r="B2" t="n">
@@ -5390,7 +5542,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>44287</v>
       </c>
       <c r="B3" t="n">
@@ -5410,7 +5562,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="3" t="n">
         <v>44317</v>
       </c>
       <c r="B4" t="n">
@@ -5430,7 +5582,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="3" t="n">
         <v>44348</v>
       </c>
       <c r="B5" t="n">
@@ -5450,7 +5602,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="3" t="n">
         <v>44378</v>
       </c>
       <c r="B6" t="n">
@@ -5470,7 +5622,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="3" t="n">
         <v>44409</v>
       </c>
       <c r="B7" t="n">
@@ -5490,7 +5642,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="3" t="n">
         <v>44440</v>
       </c>
       <c r="B8" t="n">
@@ -5510,7 +5662,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="3" t="n">
         <v>44470</v>
       </c>
       <c r="B9" t="n">
@@ -5530,7 +5682,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="3" t="n">
         <v>44501</v>
       </c>
       <c r="B10" t="n">
@@ -5550,7 +5702,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="3" t="n">
         <v>44531</v>
       </c>
       <c r="B11" t="n">
@@ -5570,7 +5722,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="3" t="n">
         <v>44621</v>
       </c>
       <c r="B12" t="n">
@@ -5590,7 +5742,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="3" t="n">
         <v>44652</v>
       </c>
       <c r="B13" t="n">
@@ -5610,7 +5762,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="3" t="n">
         <v>44682</v>
       </c>
       <c r="B14" t="n">
@@ -5630,7 +5782,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="3" t="n">
         <v>44713</v>
       </c>
       <c r="B15" t="n">
@@ -5650,7 +5802,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="3" t="n">
         <v>44743</v>
       </c>
       <c r="B16" t="n">
@@ -5670,7 +5822,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="3" t="n">
         <v>44774</v>
       </c>
       <c r="B17" t="n">
@@ -5690,7 +5842,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="3" t="n">
         <v>44805</v>
       </c>
       <c r="B18" t="n">
@@ -5710,7 +5862,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="3" t="n">
         <v>44835</v>
       </c>
       <c r="B19" t="n">
@@ -5730,7 +5882,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="3" t="n">
         <v>44866</v>
       </c>
       <c r="B20" t="n">
@@ -5750,7 +5902,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="3" t="n">
         <v>44896</v>
       </c>
       <c r="B21" t="n">
@@ -5770,7 +5922,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="3" t="n">
         <v>44986</v>
       </c>
       <c r="B22" t="n">
@@ -5790,7 +5942,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="3" t="n">
         <v>45017</v>
       </c>
       <c r="B23" t="n">
@@ -5810,7 +5962,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="3" t="n">
         <v>45047</v>
       </c>
       <c r="B24" t="n">
@@ -5830,7 +5982,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="3" t="n">
         <v>45078</v>
       </c>
       <c r="B25" t="n">
@@ -5850,7 +6002,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="3" t="n">
         <v>45108</v>
       </c>
       <c r="B26" t="n">
@@ -5870,7 +6022,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="3" t="n">
         <v>45139</v>
       </c>
       <c r="B27" t="n">
@@ -5890,7 +6042,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="3" t="n">
         <v>45170</v>
       </c>
       <c r="B28" t="n">
@@ -5910,7 +6062,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="3" t="n">
         <v>45200</v>
       </c>
       <c r="B29" t="n">
@@ -5930,7 +6082,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="n">
+      <c r="A30" s="3" t="n">
         <v>45231</v>
       </c>
       <c r="B30" t="n">
@@ -5950,7 +6102,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="n">
+      <c r="A31" s="3" t="n">
         <v>45261</v>
       </c>
       <c r="B31" t="n">
@@ -5970,7 +6122,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="n">
+      <c r="A32" s="3" t="n">
         <v>45352</v>
       </c>
       <c r="B32" t="n">
@@ -5990,7 +6142,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="n">
+      <c r="A33" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="B33" t="n">
@@ -6010,7 +6162,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="n">
+      <c r="A34" s="3" t="n">
         <v>45413</v>
       </c>
       <c r="B34" t="n">
@@ -6030,7 +6182,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="n">
+      <c r="A35" s="3" t="n">
         <v>45444</v>
       </c>
       <c r="B35" t="n">
@@ -6050,7 +6202,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="n">
+      <c r="A36" s="3" t="n">
         <v>45474</v>
       </c>
       <c r="B36" t="n">
@@ -6070,7 +6222,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="n">
+      <c r="A37" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="B37" t="n">
@@ -6090,7 +6242,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="n">
+      <c r="A38" s="3" t="n">
         <v>45536</v>
       </c>
       <c r="B38" t="n">
@@ -6110,7 +6262,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="n">
+      <c r="A39" s="3" t="n">
         <v>45566</v>
       </c>
       <c r="B39" t="n">
@@ -6130,7 +6282,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="n">
+      <c r="A40" s="3" t="n">
         <v>45597</v>
       </c>
       <c r="B40" t="n">
@@ -6150,7 +6302,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="n">
+      <c r="A41" s="3" t="n">
         <v>45627</v>
       </c>
       <c r="B41" t="n">
@@ -6170,7 +6322,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="n">
+      <c r="A42" s="3" t="n">
         <v>45717</v>
       </c>
       <c r="B42" t="n">
@@ -6190,7 +6342,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="n">
+      <c r="A43" s="3" t="n">
         <v>45748</v>
       </c>
       <c r="B43" t="n">
@@ -6210,7 +6362,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="n">
+      <c r="A44" s="3" t="n">
         <v>45778</v>
       </c>
       <c r="B44" t="n">
@@ -6230,7 +6382,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="n">
+      <c r="A45" s="3" t="n">
         <v>45809</v>
       </c>
       <c r="B45" t="n">
@@ -6250,7 +6402,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="n">
+      <c r="A46" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B46" t="n">
@@ -6270,7 +6422,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="n">
+      <c r="A47" s="3" t="n">
         <v>45870</v>
       </c>
       <c r="B47" t="n">
@@ -6290,7 +6442,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="n">
+      <c r="A48" s="3" t="n">
         <v>45901</v>
       </c>
       <c r="B48" t="n">
@@ -6310,7 +6462,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="n">
+      <c r="A49" s="3" t="n">
         <v>45931</v>
       </c>
       <c r="B49" t="n">
@@ -6330,7 +6482,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="n">
+      <c r="A50" s="3" t="n">
         <v>45962</v>
       </c>
       <c r="B50" t="n">
@@ -6350,7 +6502,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="n">
+      <c r="A51" s="3" t="n">
         <v>45992</v>
       </c>
       <c r="B51" t="n">
@@ -6370,7 +6522,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="n">
+      <c r="A52" s="3" t="n">
         <v>46082</v>
       </c>
       <c r="B52" t="n">
@@ -6390,7 +6542,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="n">
+      <c r="A53" s="3" t="n">
         <v>46113</v>
       </c>
       <c r="B53" t="n">
@@ -6410,7 +6562,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="n">
+      <c r="A54" s="3" t="n">
         <v>46143</v>
       </c>
       <c r="B54" t="n">
@@ -6430,7 +6582,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="n">
+      <c r="A55" s="3" t="n">
         <v>46174</v>
       </c>
       <c r="B55" t="n">
@@ -6450,7 +6602,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="n">
+      <c r="A56" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="B56" t="n">
@@ -6470,7 +6622,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="n">
+      <c r="A57" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="B57" t="n">
@@ -6520,7 +6672,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>44256</v>
       </c>
       <c r="B2" t="n">
@@ -6528,7 +6680,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>44287</v>
       </c>
       <c r="B3" t="n">
@@ -6536,7 +6688,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="3" t="n">
         <v>44317</v>
       </c>
       <c r="B4" t="n">
@@ -6544,7 +6696,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="3" t="n">
         <v>44348</v>
       </c>
       <c r="B5" t="n">
@@ -6552,7 +6704,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="3" t="n">
         <v>44378</v>
       </c>
       <c r="B6" t="n">
@@ -6560,7 +6712,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="3" t="n">
         <v>44409</v>
       </c>
       <c r="B7" t="n">
@@ -6568,7 +6720,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="3" t="n">
         <v>44440</v>
       </c>
       <c r="B8" t="n">
@@ -6576,7 +6728,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="3" t="n">
         <v>44470</v>
       </c>
       <c r="B9" t="n">
@@ -6584,7 +6736,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="3" t="n">
         <v>44501</v>
       </c>
       <c r="B10" t="n">
@@ -6592,7 +6744,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="3" t="n">
         <v>44531</v>
       </c>
       <c r="B11" t="n">
@@ -6600,7 +6752,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="3" t="n">
         <v>44621</v>
       </c>
       <c r="B12" t="n">
@@ -6608,7 +6760,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="3" t="n">
         <v>44652</v>
       </c>
       <c r="B13" t="n">
@@ -6616,7 +6768,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="3" t="n">
         <v>44682</v>
       </c>
       <c r="B14" t="n">
@@ -6624,7 +6776,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="3" t="n">
         <v>44713</v>
       </c>
       <c r="B15" t="n">
@@ -6632,7 +6784,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="3" t="n">
         <v>44743</v>
       </c>
       <c r="B16" t="n">
@@ -6640,7 +6792,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="3" t="n">
         <v>44774</v>
       </c>
       <c r="B17" t="n">
@@ -6648,7 +6800,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="3" t="n">
         <v>44805</v>
       </c>
       <c r="B18" t="n">
@@ -6656,7 +6808,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="3" t="n">
         <v>44835</v>
       </c>
       <c r="B19" t="n">
@@ -6664,7 +6816,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="3" t="n">
         <v>44866</v>
       </c>
       <c r="B20" t="n">
@@ -6672,7 +6824,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="3" t="n">
         <v>44896</v>
       </c>
       <c r="B21" t="n">
@@ -6680,7 +6832,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="3" t="n">
         <v>44986</v>
       </c>
       <c r="B22" t="n">
@@ -6688,7 +6840,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="3" t="n">
         <v>45017</v>
       </c>
       <c r="B23" t="n">
@@ -6696,7 +6848,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="3" t="n">
         <v>45047</v>
       </c>
       <c r="B24" t="n">
@@ -6704,7 +6856,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="3" t="n">
         <v>45078</v>
       </c>
       <c r="B25" t="n">
@@ -6712,7 +6864,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="3" t="n">
         <v>45108</v>
       </c>
       <c r="B26" t="n">
@@ -6720,7 +6872,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="3" t="n">
         <v>45139</v>
       </c>
       <c r="B27" t="n">
@@ -6728,7 +6880,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="3" t="n">
         <v>45170</v>
       </c>
       <c r="B28" t="n">
@@ -6736,7 +6888,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="3" t="n">
         <v>45200</v>
       </c>
       <c r="B29" t="n">
@@ -6744,7 +6896,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="n">
+      <c r="A30" s="3" t="n">
         <v>45231</v>
       </c>
       <c r="B30" t="n">
@@ -6752,7 +6904,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="n">
+      <c r="A31" s="3" t="n">
         <v>45261</v>
       </c>
       <c r="B31" t="n">
@@ -6760,7 +6912,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="n">
+      <c r="A32" s="3" t="n">
         <v>45352</v>
       </c>
       <c r="B32" t="n">
@@ -6768,7 +6920,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="n">
+      <c r="A33" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="B33" t="n">
@@ -6776,7 +6928,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="n">
+      <c r="A34" s="3" t="n">
         <v>45413</v>
       </c>
       <c r="B34" t="n">
@@ -6784,7 +6936,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="n">
+      <c r="A35" s="3" t="n">
         <v>45444</v>
       </c>
       <c r="B35" t="n">
@@ -6792,7 +6944,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="n">
+      <c r="A36" s="3" t="n">
         <v>45474</v>
       </c>
       <c r="B36" t="n">
@@ -6800,7 +6952,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="n">
+      <c r="A37" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="B37" t="n">
@@ -6808,7 +6960,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="n">
+      <c r="A38" s="3" t="n">
         <v>45536</v>
       </c>
       <c r="B38" t="n">
@@ -6816,7 +6968,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="n">
+      <c r="A39" s="3" t="n">
         <v>45566</v>
       </c>
       <c r="B39" t="n">
@@ -6824,7 +6976,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="n">
+      <c r="A40" s="3" t="n">
         <v>45597</v>
       </c>
       <c r="B40" t="n">
@@ -6832,7 +6984,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="n">
+      <c r="A41" s="3" t="n">
         <v>45627</v>
       </c>
       <c r="B41" t="n">
@@ -6840,7 +6992,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="n">
+      <c r="A42" s="3" t="n">
         <v>45717</v>
       </c>
       <c r="B42" t="n">
@@ -6848,7 +7000,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="n">
+      <c r="A43" s="3" t="n">
         <v>45748</v>
       </c>
       <c r="B43" t="n">
@@ -6856,7 +7008,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="n">
+      <c r="A44" s="3" t="n">
         <v>45778</v>
       </c>
       <c r="B44" t="n">
@@ -6864,7 +7016,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="n">
+      <c r="A45" s="3" t="n">
         <v>45809</v>
       </c>
       <c r="B45" t="n">
@@ -6872,7 +7024,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="n">
+      <c r="A46" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B46" t="n">
@@ -6880,7 +7032,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="n">
+      <c r="A47" s="3" t="n">
         <v>45870</v>
       </c>
       <c r="B47" t="n">
@@ -6888,7 +7040,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="n">
+      <c r="A48" s="3" t="n">
         <v>45901</v>
       </c>
       <c r="B48" t="n">
@@ -6896,7 +7048,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="n">
+      <c r="A49" s="3" t="n">
         <v>45931</v>
       </c>
       <c r="B49" t="n">
@@ -6904,7 +7056,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="n">
+      <c r="A50" s="3" t="n">
         <v>45962</v>
       </c>
       <c r="B50" t="n">
@@ -6912,7 +7064,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="n">
+      <c r="A51" s="3" t="n">
         <v>45992</v>
       </c>
       <c r="B51" t="n">
@@ -6920,7 +7072,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="n">
+      <c r="A52" s="3" t="n">
         <v>46082</v>
       </c>
       <c r="B52" t="n">
@@ -6928,7 +7080,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="n">
+      <c r="A53" s="3" t="n">
         <v>46113</v>
       </c>
       <c r="B53" t="n">
@@ -6936,7 +7088,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="n">
+      <c r="A54" s="3" t="n">
         <v>46143</v>
       </c>
       <c r="B54" t="n">
@@ -6944,7 +7096,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="n">
+      <c r="A55" s="3" t="n">
         <v>46174</v>
       </c>
       <c r="B55" t="n">
@@ -6952,7 +7104,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="n">
+      <c r="A56" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="B56" t="n">
@@ -6960,7 +7112,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="n">
+      <c r="A57" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="B57" t="n">
@@ -6998,7 +7150,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>44256</v>
       </c>
       <c r="B2" t="n">
@@ -7006,7 +7158,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>44287</v>
       </c>
       <c r="B3" t="n">
@@ -7014,7 +7166,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="3" t="n">
         <v>44317</v>
       </c>
       <c r="B4" t="n">
@@ -7022,7 +7174,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="3" t="n">
         <v>44348</v>
       </c>
       <c r="B5" t="n">
@@ -7030,7 +7182,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="3" t="n">
         <v>44378</v>
       </c>
       <c r="B6" t="n">
@@ -7038,7 +7190,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="3" t="n">
         <v>44409</v>
       </c>
       <c r="B7" t="n">
@@ -7046,7 +7198,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="3" t="n">
         <v>44440</v>
       </c>
       <c r="B8" t="n">
@@ -7054,7 +7206,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="3" t="n">
         <v>44470</v>
       </c>
       <c r="B9" t="n">
@@ -7062,7 +7214,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="3" t="n">
         <v>44501</v>
       </c>
       <c r="B10" t="n">
@@ -7070,7 +7222,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="3" t="n">
         <v>44531</v>
       </c>
       <c r="B11" t="n">
@@ -7078,7 +7230,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="3" t="n">
         <v>44621</v>
       </c>
       <c r="B12" t="n">
@@ -7086,7 +7238,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="3" t="n">
         <v>44652</v>
       </c>
       <c r="B13" t="n">
@@ -7094,7 +7246,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="3" t="n">
         <v>44682</v>
       </c>
       <c r="B14" t="n">
@@ -7102,7 +7254,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="3" t="n">
         <v>44713</v>
       </c>
       <c r="B15" t="n">
@@ -7110,7 +7262,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="3" t="n">
         <v>44743</v>
       </c>
       <c r="B16" t="n">
@@ -7118,7 +7270,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="3" t="n">
         <v>44774</v>
       </c>
       <c r="B17" t="n">
@@ -7126,7 +7278,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="3" t="n">
         <v>44805</v>
       </c>
       <c r="B18" t="n">
@@ -7134,7 +7286,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="3" t="n">
         <v>44835</v>
       </c>
       <c r="B19" t="n">
@@ -7142,7 +7294,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="3" t="n">
         <v>44866</v>
       </c>
       <c r="B20" t="n">
@@ -7150,7 +7302,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="3" t="n">
         <v>44896</v>
       </c>
       <c r="B21" t="n">
@@ -7158,7 +7310,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="3" t="n">
         <v>44986</v>
       </c>
       <c r="B22" t="n">
@@ -7166,7 +7318,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="3" t="n">
         <v>45017</v>
       </c>
       <c r="B23" t="n">
@@ -7174,7 +7326,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="3" t="n">
         <v>45047</v>
       </c>
       <c r="B24" t="n">
@@ -7182,7 +7334,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="3" t="n">
         <v>45078</v>
       </c>
       <c r="B25" t="n">
@@ -7190,7 +7342,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="3" t="n">
         <v>45108</v>
       </c>
       <c r="B26" t="n">
@@ -7198,7 +7350,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="3" t="n">
         <v>45139</v>
       </c>
       <c r="B27" t="n">
@@ -7206,7 +7358,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="3" t="n">
         <v>45170</v>
       </c>
       <c r="B28" t="n">
@@ -7214,7 +7366,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="3" t="n">
         <v>45200</v>
       </c>
       <c r="B29" t="n">
@@ -7222,7 +7374,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="n">
+      <c r="A30" s="3" t="n">
         <v>45231</v>
       </c>
       <c r="B30" t="n">
@@ -7230,7 +7382,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="n">
+      <c r="A31" s="3" t="n">
         <v>45261</v>
       </c>
       <c r="B31" t="n">
@@ -7238,7 +7390,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="n">
+      <c r="A32" s="3" t="n">
         <v>45352</v>
       </c>
       <c r="B32" t="n">
@@ -7246,7 +7398,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="n">
+      <c r="A33" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="B33" t="n">
@@ -7254,7 +7406,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="n">
+      <c r="A34" s="3" t="n">
         <v>45413</v>
       </c>
       <c r="B34" t="n">
@@ -7262,7 +7414,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="n">
+      <c r="A35" s="3" t="n">
         <v>45444</v>
       </c>
       <c r="B35" t="n">
@@ -7270,7 +7422,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="n">
+      <c r="A36" s="3" t="n">
         <v>45474</v>
       </c>
       <c r="B36" t="n">
@@ -7278,7 +7430,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="n">
+      <c r="A37" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="B37" t="n">
@@ -7286,7 +7438,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="n">
+      <c r="A38" s="3" t="n">
         <v>45536</v>
       </c>
       <c r="B38" t="n">
@@ -7294,7 +7446,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="n">
+      <c r="A39" s="3" t="n">
         <v>45566</v>
       </c>
       <c r="B39" t="n">
@@ -7302,7 +7454,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="n">
+      <c r="A40" s="3" t="n">
         <v>45597</v>
       </c>
       <c r="B40" t="n">
@@ -7310,7 +7462,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="n">
+      <c r="A41" s="3" t="n">
         <v>45627</v>
       </c>
       <c r="B41" t="n">
@@ -7318,7 +7470,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="n">
+      <c r="A42" s="3" t="n">
         <v>45717</v>
       </c>
       <c r="B42" t="n">
@@ -7326,7 +7478,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="n">
+      <c r="A43" s="3" t="n">
         <v>45748</v>
       </c>
       <c r="B43" t="n">
@@ -7334,7 +7486,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="n">
+      <c r="A44" s="3" t="n">
         <v>45778</v>
       </c>
       <c r="B44" t="n">
@@ -7342,7 +7494,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="n">
+      <c r="A45" s="3" t="n">
         <v>45809</v>
       </c>
       <c r="B45" t="n">
@@ -7350,7 +7502,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="n">
+      <c r="A46" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B46" t="n">
@@ -7358,7 +7510,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="n">
+      <c r="A47" s="3" t="n">
         <v>45870</v>
       </c>
       <c r="B47" t="n">
@@ -7366,7 +7518,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="n">
+      <c r="A48" s="3" t="n">
         <v>45901</v>
       </c>
       <c r="B48" t="n">
@@ -7374,7 +7526,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="n">
+      <c r="A49" s="3" t="n">
         <v>45931</v>
       </c>
       <c r="B49" t="n">
@@ -7382,7 +7534,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="n">
+      <c r="A50" s="3" t="n">
         <v>45962</v>
       </c>
       <c r="B50" t="n">
@@ -7390,7 +7542,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="n">
+      <c r="A51" s="3" t="n">
         <v>45992</v>
       </c>
       <c r="B51" t="n">
@@ -7398,7 +7550,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="n">
+      <c r="A52" s="3" t="n">
         <v>46082</v>
       </c>
       <c r="B52" t="n">
@@ -7406,7 +7558,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="n">
+      <c r="A53" s="3" t="n">
         <v>46113</v>
       </c>
       <c r="B53" t="n">
@@ -7414,7 +7566,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="n">
+      <c r="A54" s="3" t="n">
         <v>46143</v>
       </c>
       <c r="B54" t="n">
@@ -7422,7 +7574,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="n">
+      <c r="A55" s="3" t="n">
         <v>46174</v>
       </c>
       <c r="B55" t="n">
@@ -7430,7 +7582,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="n">
+      <c r="A56" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="B56" t="n">
@@ -7438,7 +7590,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="n">
+      <c r="A57" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="B57" t="n">
@@ -7476,7 +7628,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>44256</v>
       </c>
       <c r="B2" t="n">
@@ -7484,7 +7636,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>44287</v>
       </c>
       <c r="B3" t="n">
@@ -7492,7 +7644,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="3" t="n">
         <v>44317</v>
       </c>
       <c r="B4" t="n">
@@ -7500,7 +7652,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="3" t="n">
         <v>44348</v>
       </c>
       <c r="B5" t="n">
@@ -7508,7 +7660,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="3" t="n">
         <v>44378</v>
       </c>
       <c r="B6" t="n">
@@ -7516,7 +7668,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="3" t="n">
         <v>44409</v>
       </c>
       <c r="B7" t="n">
@@ -7524,7 +7676,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="3" t="n">
         <v>44440</v>
       </c>
       <c r="B8" t="n">
@@ -7532,7 +7684,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="3" t="n">
         <v>44470</v>
       </c>
       <c r="B9" t="n">
@@ -7540,7 +7692,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="3" t="n">
         <v>44501</v>
       </c>
       <c r="B10" t="n">
@@ -7548,7 +7700,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="3" t="n">
         <v>44531</v>
       </c>
       <c r="B11" t="n">
@@ -7556,7 +7708,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="3" t="n">
         <v>44621</v>
       </c>
       <c r="B12" t="n">
@@ -7564,7 +7716,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="3" t="n">
         <v>44652</v>
       </c>
       <c r="B13" t="n">
@@ -7572,7 +7724,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="3" t="n">
         <v>44682</v>
       </c>
       <c r="B14" t="n">
@@ -7580,7 +7732,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="3" t="n">
         <v>44713</v>
       </c>
       <c r="B15" t="n">
@@ -7588,7 +7740,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="3" t="n">
         <v>44743</v>
       </c>
       <c r="B16" t="n">
@@ -7596,7 +7748,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="3" t="n">
         <v>44774</v>
       </c>
       <c r="B17" t="n">
@@ -7604,7 +7756,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="3" t="n">
         <v>44805</v>
       </c>
       <c r="B18" t="n">
@@ -7612,7 +7764,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="3" t="n">
         <v>44835</v>
       </c>
       <c r="B19" t="n">
@@ -7620,7 +7772,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="3" t="n">
         <v>44866</v>
       </c>
       <c r="B20" t="n">
@@ -7628,7 +7780,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="3" t="n">
         <v>44896</v>
       </c>
       <c r="B21" t="n">
@@ -7636,7 +7788,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="3" t="n">
         <v>44986</v>
       </c>
       <c r="B22" t="n">
@@ -7644,7 +7796,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="3" t="n">
         <v>45017</v>
       </c>
       <c r="B23" t="n">
@@ -7652,7 +7804,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="3" t="n">
         <v>45047</v>
       </c>
       <c r="B24" t="n">
@@ -7660,7 +7812,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="3" t="n">
         <v>45078</v>
       </c>
       <c r="B25" t="n">
@@ -7668,7 +7820,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="3" t="n">
         <v>45108</v>
       </c>
       <c r="B26" t="n">
@@ -7676,7 +7828,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="3" t="n">
         <v>45139</v>
       </c>
       <c r="B27" t="n">
@@ -7684,7 +7836,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="3" t="n">
         <v>45170</v>
       </c>
       <c r="B28" t="n">
@@ -7692,7 +7844,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="3" t="n">
         <v>45200</v>
       </c>
       <c r="B29" t="n">
@@ -7700,7 +7852,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="n">
+      <c r="A30" s="3" t="n">
         <v>45231</v>
       </c>
       <c r="B30" t="n">
@@ -7708,7 +7860,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="n">
+      <c r="A31" s="3" t="n">
         <v>45261</v>
       </c>
       <c r="B31" t="n">
@@ -7716,7 +7868,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="n">
+      <c r="A32" s="3" t="n">
         <v>45352</v>
       </c>
       <c r="B32" t="n">
@@ -7724,7 +7876,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="n">
+      <c r="A33" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="B33" t="n">
@@ -7732,7 +7884,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="n">
+      <c r="A34" s="3" t="n">
         <v>45413</v>
       </c>
       <c r="B34" t="n">
@@ -7740,7 +7892,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="n">
+      <c r="A35" s="3" t="n">
         <v>45444</v>
       </c>
       <c r="B35" t="n">
@@ -7748,7 +7900,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="n">
+      <c r="A36" s="3" t="n">
         <v>45474</v>
       </c>
       <c r="B36" t="n">
@@ -7756,7 +7908,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="n">
+      <c r="A37" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="B37" t="n">
@@ -7764,7 +7916,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="n">
+      <c r="A38" s="3" t="n">
         <v>45536</v>
       </c>
       <c r="B38" t="n">
@@ -7772,7 +7924,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="n">
+      <c r="A39" s="3" t="n">
         <v>45566</v>
       </c>
       <c r="B39" t="n">
@@ -7780,7 +7932,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="n">
+      <c r="A40" s="3" t="n">
         <v>45597</v>
       </c>
       <c r="B40" t="n">
@@ -7788,7 +7940,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="n">
+      <c r="A41" s="3" t="n">
         <v>45627</v>
       </c>
       <c r="B41" t="n">
@@ -7796,7 +7948,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="n">
+      <c r="A42" s="3" t="n">
         <v>45717</v>
       </c>
       <c r="B42" t="n">
@@ -7804,7 +7956,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="n">
+      <c r="A43" s="3" t="n">
         <v>45748</v>
       </c>
       <c r="B43" t="n">
@@ -7812,7 +7964,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="n">
+      <c r="A44" s="3" t="n">
         <v>45778</v>
       </c>
       <c r="B44" t="n">
@@ -7820,7 +7972,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="n">
+      <c r="A45" s="3" t="n">
         <v>45809</v>
       </c>
       <c r="B45" t="n">
@@ -7828,7 +7980,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="n">
+      <c r="A46" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B46" t="n">
@@ -7836,7 +7988,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="n">
+      <c r="A47" s="3" t="n">
         <v>45870</v>
       </c>
       <c r="B47" t="n">
@@ -7844,7 +7996,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="n">
+      <c r="A48" s="3" t="n">
         <v>45901</v>
       </c>
       <c r="B48" t="n">
@@ -7852,7 +8004,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="n">
+      <c r="A49" s="3" t="n">
         <v>45931</v>
       </c>
       <c r="B49" t="n">
@@ -7860,7 +8012,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="n">
+      <c r="A50" s="3" t="n">
         <v>45962</v>
       </c>
       <c r="B50" t="n">
@@ -7868,7 +8020,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="n">
+      <c r="A51" s="3" t="n">
         <v>45992</v>
       </c>
       <c r="B51" t="n">
@@ -7876,7 +8028,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="n">
+      <c r="A52" s="3" t="n">
         <v>46082</v>
       </c>
       <c r="B52" t="n">
@@ -7884,7 +8036,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="n">
+      <c r="A53" s="3" t="n">
         <v>46113</v>
       </c>
       <c r="B53" t="n">
@@ -7892,7 +8044,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="n">
+      <c r="A54" s="3" t="n">
         <v>46143</v>
       </c>
       <c r="B54" t="n">
@@ -7900,7 +8052,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="n">
+      <c r="A55" s="3" t="n">
         <v>46174</v>
       </c>
       <c r="B55" t="n">
@@ -7908,7 +8060,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="n">
+      <c r="A56" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="B56" t="n">
@@ -7916,7 +8068,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="n">
+      <c r="A57" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="B57" t="n">
@@ -7954,7 +8106,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>44256</v>
       </c>
       <c r="B2" t="n">
@@ -7962,7 +8114,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>44287</v>
       </c>
       <c r="B3" t="n">
@@ -7970,7 +8122,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="3" t="n">
         <v>44317</v>
       </c>
       <c r="B4" t="n">
@@ -7978,7 +8130,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="3" t="n">
         <v>44348</v>
       </c>
       <c r="B5" t="n">
@@ -7986,7 +8138,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="3" t="n">
         <v>44378</v>
       </c>
       <c r="B6" t="n">
@@ -7994,7 +8146,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="3" t="n">
         <v>44409</v>
       </c>
       <c r="B7" t="n">
@@ -8002,7 +8154,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="3" t="n">
         <v>44440</v>
       </c>
       <c r="B8" t="n">
@@ -8010,7 +8162,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="3" t="n">
         <v>44470</v>
       </c>
       <c r="B9" t="n">
@@ -8018,7 +8170,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="3" t="n">
         <v>44501</v>
       </c>
       <c r="B10" t="n">
@@ -8026,7 +8178,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="3" t="n">
         <v>44531</v>
       </c>
       <c r="B11" t="n">
@@ -8034,7 +8186,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="3" t="n">
         <v>44621</v>
       </c>
       <c r="B12" t="n">
@@ -8042,7 +8194,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="3" t="n">
         <v>44652</v>
       </c>
       <c r="B13" t="n">
@@ -8050,7 +8202,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="3" t="n">
         <v>44682</v>
       </c>
       <c r="B14" t="n">
@@ -8058,7 +8210,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="3" t="n">
         <v>44713</v>
       </c>
       <c r="B15" t="n">
@@ -8066,7 +8218,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="3" t="n">
         <v>44743</v>
       </c>
       <c r="B16" t="n">
@@ -8074,7 +8226,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="3" t="n">
         <v>44774</v>
       </c>
       <c r="B17" t="n">
@@ -8082,7 +8234,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="3" t="n">
         <v>44805</v>
       </c>
       <c r="B18" t="n">
@@ -8090,7 +8242,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="3" t="n">
         <v>44835</v>
       </c>
       <c r="B19" t="n">
@@ -8098,7 +8250,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="3" t="n">
         <v>44866</v>
       </c>
       <c r="B20" t="n">
@@ -8106,7 +8258,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="3" t="n">
         <v>44896</v>
       </c>
       <c r="B21" t="n">
@@ -8114,7 +8266,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="3" t="n">
         <v>44986</v>
       </c>
       <c r="B22" t="n">
@@ -8122,7 +8274,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="3" t="n">
         <v>45017</v>
       </c>
       <c r="B23" t="n">
@@ -8130,7 +8282,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="3" t="n">
         <v>45047</v>
       </c>
       <c r="B24" t="n">
@@ -8138,7 +8290,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="3" t="n">
         <v>45078</v>
       </c>
       <c r="B25" t="n">
@@ -8146,7 +8298,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="3" t="n">
         <v>45108</v>
       </c>
       <c r="B26" t="n">
@@ -8154,7 +8306,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="3" t="n">
         <v>45139</v>
       </c>
       <c r="B27" t="n">
@@ -8162,7 +8314,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="3" t="n">
         <v>45170</v>
       </c>
       <c r="B28" t="n">
@@ -8170,7 +8322,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="3" t="n">
         <v>45200</v>
       </c>
       <c r="B29" t="n">
@@ -8178,7 +8330,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="n">
+      <c r="A30" s="3" t="n">
         <v>45231</v>
       </c>
       <c r="B30" t="n">
@@ -8186,7 +8338,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="n">
+      <c r="A31" s="3" t="n">
         <v>45261</v>
       </c>
       <c r="B31" t="n">
@@ -8194,7 +8346,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="n">
+      <c r="A32" s="3" t="n">
         <v>45352</v>
       </c>
       <c r="B32" t="n">
@@ -8202,7 +8354,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="n">
+      <c r="A33" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="B33" t="n">
@@ -8210,7 +8362,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="n">
+      <c r="A34" s="3" t="n">
         <v>45413</v>
       </c>
       <c r="B34" t="n">
@@ -8218,7 +8370,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="n">
+      <c r="A35" s="3" t="n">
         <v>45444</v>
       </c>
       <c r="B35" t="n">
@@ -8226,7 +8378,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="n">
+      <c r="A36" s="3" t="n">
         <v>45474</v>
       </c>
       <c r="B36" t="n">
@@ -8234,7 +8386,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="n">
+      <c r="A37" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="B37" t="n">
@@ -8242,7 +8394,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="n">
+      <c r="A38" s="3" t="n">
         <v>45536</v>
       </c>
       <c r="B38" t="n">
@@ -8250,7 +8402,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="n">
+      <c r="A39" s="3" t="n">
         <v>45566</v>
       </c>
       <c r="B39" t="n">
@@ -8258,7 +8410,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="n">
+      <c r="A40" s="3" t="n">
         <v>45597</v>
       </c>
       <c r="B40" t="n">
@@ -8266,7 +8418,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="n">
+      <c r="A41" s="3" t="n">
         <v>45627</v>
       </c>
       <c r="B41" t="n">
@@ -8274,7 +8426,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="n">
+      <c r="A42" s="3" t="n">
         <v>45717</v>
       </c>
       <c r="B42" t="n">
@@ -8282,7 +8434,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="n">
+      <c r="A43" s="3" t="n">
         <v>45748</v>
       </c>
       <c r="B43" t="n">
@@ -8290,7 +8442,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="n">
+      <c r="A44" s="3" t="n">
         <v>45778</v>
       </c>
       <c r="B44" t="n">
@@ -8298,7 +8450,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="n">
+      <c r="A45" s="3" t="n">
         <v>45809</v>
       </c>
       <c r="B45" t="n">
@@ -8306,7 +8458,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="n">
+      <c r="A46" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B46" t="n">
@@ -8314,7 +8466,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="n">
+      <c r="A47" s="3" t="n">
         <v>45870</v>
       </c>
       <c r="B47" t="n">
@@ -8322,7 +8474,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="n">
+      <c r="A48" s="3" t="n">
         <v>45901</v>
       </c>
       <c r="B48" t="n">
@@ -8330,7 +8482,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="n">
+      <c r="A49" s="3" t="n">
         <v>45931</v>
       </c>
       <c r="B49" t="n">
@@ -8338,7 +8490,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="n">
+      <c r="A50" s="3" t="n">
         <v>45962</v>
       </c>
       <c r="B50" t="n">
@@ -8346,7 +8498,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="n">
+      <c r="A51" s="3" t="n">
         <v>45992</v>
       </c>
       <c r="B51" t="n">
@@ -8354,7 +8506,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="n">
+      <c r="A52" s="3" t="n">
         <v>46082</v>
       </c>
       <c r="B52" t="n">
@@ -8362,7 +8514,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="n">
+      <c r="A53" s="3" t="n">
         <v>46113</v>
       </c>
       <c r="B53" t="n">
@@ -8370,7 +8522,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="n">
+      <c r="A54" s="3" t="n">
         <v>46143</v>
       </c>
       <c r="B54" t="n">
@@ -8378,7 +8530,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="n">
+      <c r="A55" s="3" t="n">
         <v>46174</v>
       </c>
       <c r="B55" t="n">
@@ -8386,7 +8538,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="n">
+      <c r="A56" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="B56" t="n">
@@ -8394,7 +8546,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="n">
+      <c r="A57" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="B57" t="n">
@@ -8437,7 +8589,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>44256</v>
       </c>
       <c r="C2" t="n">
@@ -8445,7 +8597,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>44287</v>
       </c>
       <c r="C3" t="n">
@@ -8453,7 +8605,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="3" t="n">
         <v>44317</v>
       </c>
       <c r="C4" t="n">
@@ -8461,7 +8613,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="3" t="n">
         <v>44348</v>
       </c>
       <c r="C5" t="n">
@@ -8469,7 +8621,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="3" t="n">
         <v>44378</v>
       </c>
       <c r="C6" t="n">
@@ -8477,7 +8629,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="3" t="n">
         <v>44409</v>
       </c>
       <c r="C7" t="n">
@@ -8485,7 +8637,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="3" t="n">
         <v>44440</v>
       </c>
       <c r="C8" t="n">
@@ -8493,7 +8645,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="3" t="n">
         <v>44470</v>
       </c>
       <c r="C9" t="n">
@@ -8501,7 +8653,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="3" t="n">
         <v>44501</v>
       </c>
       <c r="C10" t="n">
@@ -8509,7 +8661,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="3" t="n">
         <v>44531</v>
       </c>
       <c r="C11" t="n">
@@ -8517,7 +8669,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="3" t="n">
         <v>44621</v>
       </c>
       <c r="C12" t="n">
@@ -8525,7 +8677,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="3" t="n">
         <v>44652</v>
       </c>
       <c r="C13" t="n">
@@ -8533,7 +8685,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="3" t="n">
         <v>44682</v>
       </c>
       <c r="C14" t="n">
@@ -8541,7 +8693,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="3" t="n">
         <v>44713</v>
       </c>
       <c r="C15" t="n">
@@ -8549,7 +8701,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="3" t="n">
         <v>44743</v>
       </c>
       <c r="C16" t="n">
@@ -8557,7 +8709,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="3" t="n">
         <v>44774</v>
       </c>
       <c r="C17" t="n">
@@ -8565,7 +8717,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="3" t="n">
         <v>44805</v>
       </c>
       <c r="C18" t="n">
@@ -8573,7 +8725,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="3" t="n">
         <v>44835</v>
       </c>
       <c r="C19" t="n">
@@ -8581,7 +8733,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="3" t="n">
         <v>44866</v>
       </c>
       <c r="C20" t="n">
@@ -8589,7 +8741,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="3" t="n">
         <v>44896</v>
       </c>
       <c r="C21" t="n">
@@ -8597,7 +8749,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="3" t="n">
         <v>44986</v>
       </c>
       <c r="B22" t="n">
@@ -8608,7 +8760,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="3" t="n">
         <v>45017</v>
       </c>
       <c r="B23" t="n">
@@ -8619,7 +8771,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="3" t="n">
         <v>45047</v>
       </c>
       <c r="B24" t="n">
@@ -8630,7 +8782,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="3" t="n">
         <v>45078</v>
       </c>
       <c r="B25" t="n">
@@ -8641,7 +8793,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="3" t="n">
         <v>45108</v>
       </c>
       <c r="B26" t="n">
@@ -8652,7 +8804,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="3" t="n">
         <v>45139</v>
       </c>
       <c r="B27" t="n">
@@ -8663,7 +8815,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="3" t="n">
         <v>45170</v>
       </c>
       <c r="B28" t="n">
@@ -8674,7 +8826,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="3" t="n">
         <v>45200</v>
       </c>
       <c r="B29" t="n">
@@ -8685,7 +8837,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="n">
+      <c r="A30" s="3" t="n">
         <v>45231</v>
       </c>
       <c r="B30" t="n">
@@ -8696,7 +8848,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="n">
+      <c r="A31" s="3" t="n">
         <v>45261</v>
       </c>
       <c r="B31" t="n">
@@ -8707,7 +8859,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="n">
+      <c r="A32" s="3" t="n">
         <v>45352</v>
       </c>
       <c r="B32" t="n">
@@ -8718,7 +8870,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="n">
+      <c r="A33" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="B33" t="n">
@@ -8729,7 +8881,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="n">
+      <c r="A34" s="3" t="n">
         <v>45413</v>
       </c>
       <c r="B34" t="n">
@@ -8740,7 +8892,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="n">
+      <c r="A35" s="3" t="n">
         <v>45444</v>
       </c>
       <c r="B35" t="n">
@@ -8751,7 +8903,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="n">
+      <c r="A36" s="3" t="n">
         <v>45474</v>
       </c>
       <c r="B36" t="n">
@@ -8762,7 +8914,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="n">
+      <c r="A37" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="B37" t="n">
@@ -8773,7 +8925,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="n">
+      <c r="A38" s="3" t="n">
         <v>45536</v>
       </c>
       <c r="B38" t="n">
@@ -8784,7 +8936,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="n">
+      <c r="A39" s="3" t="n">
         <v>45566</v>
       </c>
       <c r="B39" t="n">
@@ -8795,7 +8947,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="n">
+      <c r="A40" s="3" t="n">
         <v>45597</v>
       </c>
       <c r="B40" t="n">
@@ -8806,7 +8958,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="n">
+      <c r="A41" s="3" t="n">
         <v>45627</v>
       </c>
       <c r="B41" t="n">
@@ -8817,7 +8969,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="n">
+      <c r="A42" s="3" t="n">
         <v>45717</v>
       </c>
       <c r="B42" t="n">
@@ -8828,7 +8980,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="n">
+      <c r="A43" s="3" t="n">
         <v>45748</v>
       </c>
       <c r="B43" t="n">
@@ -8839,7 +8991,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="n">
+      <c r="A44" s="3" t="n">
         <v>45778</v>
       </c>
       <c r="B44" t="n">
@@ -8850,7 +9002,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="n">
+      <c r="A45" s="3" t="n">
         <v>45809</v>
       </c>
       <c r="B45" t="n">
@@ -8861,7 +9013,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="n">
+      <c r="A46" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B46" t="n">
@@ -8872,7 +9024,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="n">
+      <c r="A47" s="3" t="n">
         <v>45870</v>
       </c>
       <c r="B47" t="n">
@@ -8883,7 +9035,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="n">
+      <c r="A48" s="3" t="n">
         <v>45901</v>
       </c>
       <c r="B48" t="n">
@@ -8894,7 +9046,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="n">
+      <c r="A49" s="3" t="n">
         <v>45931</v>
       </c>
       <c r="B49" t="n">
@@ -8905,7 +9057,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="n">
+      <c r="A50" s="3" t="n">
         <v>45962</v>
       </c>
       <c r="B50" t="n">
@@ -8916,7 +9068,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="n">
+      <c r="A51" s="3" t="n">
         <v>45992</v>
       </c>
       <c r="B51" t="n">
@@ -8927,7 +9079,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="n">
+      <c r="A52" s="3" t="n">
         <v>46082</v>
       </c>
       <c r="B52" t="n">
@@ -8938,7 +9090,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="n">
+      <c r="A53" s="3" t="n">
         <v>46113</v>
       </c>
       <c r="B53" t="n">
@@ -8949,7 +9101,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="n">
+      <c r="A54" s="3" t="n">
         <v>46143</v>
       </c>
       <c r="B54" t="n">
@@ -8960,7 +9112,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="n">
+      <c r="A55" s="3" t="n">
         <v>46174</v>
       </c>
       <c r="B55" t="n">
@@ -8971,7 +9123,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="n">
+      <c r="A56" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="B56" t="n">
@@ -8982,7 +9134,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="n">
+      <c r="A57" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="B57" t="n">
@@ -9028,7 +9180,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>44256</v>
       </c>
       <c r="B2" t="n">
@@ -9039,7 +9191,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>44287</v>
       </c>
       <c r="B3" t="n">
@@ -9050,7 +9202,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="3" t="n">
         <v>44317</v>
       </c>
       <c r="B4" t="n">
@@ -9061,7 +9213,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="3" t="n">
         <v>44348</v>
       </c>
       <c r="B5" t="n">
@@ -9072,7 +9224,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="3" t="n">
         <v>44378</v>
       </c>
       <c r="B6" t="n">
@@ -9083,7 +9235,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="3" t="n">
         <v>44409</v>
       </c>
       <c r="B7" t="n">
@@ -9094,7 +9246,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="3" t="n">
         <v>44440</v>
       </c>
       <c r="B8" t="n">
@@ -9105,7 +9257,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="3" t="n">
         <v>44470</v>
       </c>
       <c r="B9" t="n">
@@ -9116,7 +9268,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="3" t="n">
         <v>44501</v>
       </c>
       <c r="B10" t="n">
@@ -9127,7 +9279,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="3" t="n">
         <v>44531</v>
       </c>
       <c r="B11" t="n">
@@ -9138,7 +9290,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="3" t="n">
         <v>44621</v>
       </c>
       <c r="B12" t="n">
@@ -9149,7 +9301,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="3" t="n">
         <v>44652</v>
       </c>
       <c r="B13" t="n">
@@ -9160,7 +9312,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="3" t="n">
         <v>44682</v>
       </c>
       <c r="B14" t="n">
@@ -9171,7 +9323,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="3" t="n">
         <v>44713</v>
       </c>
       <c r="B15" t="n">
@@ -9182,7 +9334,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="3" t="n">
         <v>44743</v>
       </c>
       <c r="B16" t="n">
@@ -9193,7 +9345,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="3" t="n">
         <v>44774</v>
       </c>
       <c r="B17" t="n">
@@ -9204,7 +9356,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="3" t="n">
         <v>44805</v>
       </c>
       <c r="B18" t="n">
@@ -9215,7 +9367,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="3" t="n">
         <v>44835</v>
       </c>
       <c r="B19" t="n">
@@ -9226,7 +9378,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="3" t="n">
         <v>44866</v>
       </c>
       <c r="B20" t="n">
@@ -9237,7 +9389,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="3" t="n">
         <v>44896</v>
       </c>
       <c r="B21" t="n">
@@ -9248,7 +9400,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="3" t="n">
         <v>44986</v>
       </c>
       <c r="B22" t="n">
@@ -9259,7 +9411,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="3" t="n">
         <v>45017</v>
       </c>
       <c r="B23" t="n">
@@ -9270,7 +9422,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="3" t="n">
         <v>45047</v>
       </c>
       <c r="B24" t="n">
@@ -9281,7 +9433,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="3" t="n">
         <v>45078</v>
       </c>
       <c r="B25" t="n">
@@ -9292,7 +9444,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="3" t="n">
         <v>45108</v>
       </c>
       <c r="B26" t="n">
@@ -9303,7 +9455,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="3" t="n">
         <v>45139</v>
       </c>
       <c r="B27" t="n">
@@ -9314,7 +9466,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="3" t="n">
         <v>45170</v>
       </c>
       <c r="B28" t="n">
@@ -9325,7 +9477,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="3" t="n">
         <v>45200</v>
       </c>
       <c r="B29" t="n">
@@ -9336,7 +9488,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="n">
+      <c r="A30" s="3" t="n">
         <v>45231</v>
       </c>
       <c r="B30" t="n">
@@ -9347,7 +9499,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="n">
+      <c r="A31" s="3" t="n">
         <v>45261</v>
       </c>
       <c r="B31" t="n">
@@ -9358,7 +9510,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="n">
+      <c r="A32" s="3" t="n">
         <v>45352</v>
       </c>
       <c r="B32" t="n">
@@ -9369,7 +9521,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="n">
+      <c r="A33" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="B33" t="n">
@@ -9380,7 +9532,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="n">
+      <c r="A34" s="3" t="n">
         <v>45413</v>
       </c>
       <c r="B34" t="n">
@@ -9391,7 +9543,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="n">
+      <c r="A35" s="3" t="n">
         <v>45444</v>
       </c>
       <c r="B35" t="n">
@@ -9402,7 +9554,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="n">
+      <c r="A36" s="3" t="n">
         <v>45474</v>
       </c>
       <c r="B36" t="n">
@@ -9413,7 +9565,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="n">
+      <c r="A37" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="B37" t="n">
@@ -9424,7 +9576,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="n">
+      <c r="A38" s="3" t="n">
         <v>45536</v>
       </c>
       <c r="B38" t="n">
@@ -9435,7 +9587,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="n">
+      <c r="A39" s="3" t="n">
         <v>45566</v>
       </c>
       <c r="B39" t="n">
@@ -9446,7 +9598,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="n">
+      <c r="A40" s="3" t="n">
         <v>45597</v>
       </c>
       <c r="B40" t="n">
@@ -9457,7 +9609,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="n">
+      <c r="A41" s="3" t="n">
         <v>45627</v>
       </c>
       <c r="B41" t="n">
@@ -9468,7 +9620,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="n">
+      <c r="A42" s="3" t="n">
         <v>45717</v>
       </c>
       <c r="B42" t="n">
@@ -9479,7 +9631,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="n">
+      <c r="A43" s="3" t="n">
         <v>45748</v>
       </c>
       <c r="B43" t="n">
@@ -9490,7 +9642,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="n">
+      <c r="A44" s="3" t="n">
         <v>45778</v>
       </c>
       <c r="B44" t="n">
@@ -9501,7 +9653,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="n">
+      <c r="A45" s="3" t="n">
         <v>45809</v>
       </c>
       <c r="B45" t="n">
@@ -9512,7 +9664,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="n">
+      <c r="A46" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B46" t="n">
@@ -9523,7 +9675,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="n">
+      <c r="A47" s="3" t="n">
         <v>45870</v>
       </c>
       <c r="B47" t="n">
@@ -9534,7 +9686,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="n">
+      <c r="A48" s="3" t="n">
         <v>45901</v>
       </c>
       <c r="B48" t="n">
@@ -9545,7 +9697,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="n">
+      <c r="A49" s="3" t="n">
         <v>45931</v>
       </c>
       <c r="B49" t="n">
@@ -9556,7 +9708,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="n">
+      <c r="A50" s="3" t="n">
         <v>45962</v>
       </c>
       <c r="B50" t="n">
@@ -9567,7 +9719,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="n">
+      <c r="A51" s="3" t="n">
         <v>45992</v>
       </c>
       <c r="B51" t="n">
@@ -9578,7 +9730,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="n">
+      <c r="A52" s="3" t="n">
         <v>46082</v>
       </c>
       <c r="B52" t="n">
@@ -9589,7 +9741,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="n">
+      <c r="A53" s="3" t="n">
         <v>46113</v>
       </c>
       <c r="B53" t="n">
@@ -9600,7 +9752,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="n">
+      <c r="A54" s="3" t="n">
         <v>46143</v>
       </c>
       <c r="B54" t="n">
@@ -9611,7 +9763,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="n">
+      <c r="A55" s="3" t="n">
         <v>46174</v>
       </c>
       <c r="B55" t="n">
@@ -9622,7 +9774,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="n">
+      <c r="A56" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="B56" t="n">
@@ -9633,7 +9785,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="n">
+      <c r="A57" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="B57" t="n">
@@ -9674,7 +9826,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>44256</v>
       </c>
       <c r="B2" t="n">
@@ -9682,7 +9834,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>44287</v>
       </c>
       <c r="B3" t="n">
@@ -9690,7 +9842,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="3" t="n">
         <v>44317</v>
       </c>
       <c r="B4" t="n">
@@ -9698,7 +9850,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="3" t="n">
         <v>44348</v>
       </c>
       <c r="B5" t="n">
@@ -9706,7 +9858,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="3" t="n">
         <v>44378</v>
       </c>
       <c r="B6" t="n">
@@ -9714,7 +9866,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="3" t="n">
         <v>44409</v>
       </c>
       <c r="B7" t="n">
@@ -9722,7 +9874,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="3" t="n">
         <v>44440</v>
       </c>
       <c r="B8" t="n">
@@ -9730,7 +9882,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="3" t="n">
         <v>44470</v>
       </c>
       <c r="B9" t="n">
@@ -9738,7 +9890,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="3" t="n">
         <v>44501</v>
       </c>
       <c r="B10" t="n">
@@ -9746,7 +9898,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="3" t="n">
         <v>44531</v>
       </c>
       <c r="B11" t="n">
@@ -9754,7 +9906,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="3" t="n">
         <v>44621</v>
       </c>
       <c r="B12" t="n">
@@ -9762,7 +9914,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="3" t="n">
         <v>44652</v>
       </c>
       <c r="B13" t="n">
@@ -9770,7 +9922,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="3" t="n">
         <v>44682</v>
       </c>
       <c r="B14" t="n">
@@ -9778,7 +9930,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="3" t="n">
         <v>44713</v>
       </c>
       <c r="B15" t="n">
@@ -9786,7 +9938,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="3" t="n">
         <v>44743</v>
       </c>
       <c r="B16" t="n">
@@ -9794,7 +9946,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="3" t="n">
         <v>44774</v>
       </c>
       <c r="B17" t="n">
@@ -9802,7 +9954,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="3" t="n">
         <v>44805</v>
       </c>
       <c r="B18" t="n">
@@ -9810,7 +9962,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="3" t="n">
         <v>44835</v>
       </c>
       <c r="B19" t="n">
@@ -9818,7 +9970,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="3" t="n">
         <v>44866</v>
       </c>
       <c r="B20" t="n">
@@ -9826,7 +9978,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="3" t="n">
         <v>44896</v>
       </c>
       <c r="B21" t="n">
@@ -9834,7 +9986,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="3" t="n">
         <v>44986</v>
       </c>
       <c r="B22" t="n">
@@ -9842,7 +9994,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="3" t="n">
         <v>45017</v>
       </c>
       <c r="B23" t="n">
@@ -9850,7 +10002,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="3" t="n">
         <v>45047</v>
       </c>
       <c r="B24" t="n">
@@ -9858,7 +10010,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="3" t="n">
         <v>45078</v>
       </c>
       <c r="B25" t="n">
@@ -9866,7 +10018,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="3" t="n">
         <v>45108</v>
       </c>
       <c r="B26" t="n">
@@ -9874,7 +10026,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="3" t="n">
         <v>45139</v>
       </c>
       <c r="B27" t="n">
@@ -9882,7 +10034,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="3" t="n">
         <v>45170</v>
       </c>
       <c r="B28" t="n">
@@ -9890,7 +10042,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="3" t="n">
         <v>45200</v>
       </c>
       <c r="B29" t="n">
@@ -9898,7 +10050,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="n">
+      <c r="A30" s="3" t="n">
         <v>45231</v>
       </c>
       <c r="B30" t="n">
@@ -9906,7 +10058,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="n">
+      <c r="A31" s="3" t="n">
         <v>45261</v>
       </c>
       <c r="B31" t="n">
@@ -9914,7 +10066,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="n">
+      <c r="A32" s="3" t="n">
         <v>45352</v>
       </c>
       <c r="B32" t="n">
@@ -9922,7 +10074,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="n">
+      <c r="A33" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="B33" t="n">
@@ -9930,7 +10082,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="n">
+      <c r="A34" s="3" t="n">
         <v>45413</v>
       </c>
       <c r="B34" t="n">
@@ -9938,7 +10090,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="n">
+      <c r="A35" s="3" t="n">
         <v>45444</v>
       </c>
       <c r="B35" t="n">
@@ -9946,7 +10098,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="n">
+      <c r="A36" s="3" t="n">
         <v>45474</v>
       </c>
       <c r="B36" t="n">
@@ -9954,7 +10106,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="n">
+      <c r="A37" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="B37" t="n">
@@ -9962,7 +10114,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="n">
+      <c r="A38" s="3" t="n">
         <v>45536</v>
       </c>
       <c r="B38" t="n">
@@ -9970,7 +10122,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="n">
+      <c r="A39" s="3" t="n">
         <v>45566</v>
       </c>
       <c r="B39" t="n">
@@ -9978,7 +10130,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="n">
+      <c r="A40" s="3" t="n">
         <v>45597</v>
       </c>
       <c r="B40" t="n">
@@ -9986,7 +10138,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="n">
+      <c r="A41" s="3" t="n">
         <v>45627</v>
       </c>
       <c r="B41" t="n">
@@ -9994,7 +10146,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="n">
+      <c r="A42" s="3" t="n">
         <v>45717</v>
       </c>
       <c r="B42" t="n">
@@ -10002,7 +10154,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="n">
+      <c r="A43" s="3" t="n">
         <v>45748</v>
       </c>
       <c r="B43" t="n">
@@ -10010,7 +10162,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="n">
+      <c r="A44" s="3" t="n">
         <v>45778</v>
       </c>
       <c r="B44" t="n">
@@ -10018,7 +10170,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="n">
+      <c r="A45" s="3" t="n">
         <v>45809</v>
       </c>
       <c r="B45" t="n">
@@ -10026,7 +10178,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="n">
+      <c r="A46" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B46" t="n">
@@ -10034,7 +10186,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="n">
+      <c r="A47" s="3" t="n">
         <v>45870</v>
       </c>
       <c r="B47" t="n">
@@ -10042,7 +10194,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="n">
+      <c r="A48" s="3" t="n">
         <v>45901</v>
       </c>
       <c r="B48" t="n">
@@ -10050,7 +10202,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="n">
+      <c r="A49" s="3" t="n">
         <v>45931</v>
       </c>
       <c r="B49" t="n">
@@ -10058,7 +10210,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="n">
+      <c r="A50" s="3" t="n">
         <v>45962</v>
       </c>
       <c r="B50" t="n">
@@ -10066,7 +10218,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="n">
+      <c r="A51" s="3" t="n">
         <v>45992</v>
       </c>
       <c r="B51" t="n">
@@ -10074,7 +10226,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="n">
+      <c r="A52" s="3" t="n">
         <v>46082</v>
       </c>
       <c r="B52" t="n">
@@ -10082,7 +10234,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="n">
+      <c r="A53" s="3" t="n">
         <v>46113</v>
       </c>
       <c r="B53" t="n">
@@ -10090,7 +10242,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="n">
+      <c r="A54" s="3" t="n">
         <v>46143</v>
       </c>
       <c r="B54" t="n">
@@ -10098,7 +10250,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="n">
+      <c r="A55" s="3" t="n">
         <v>46174</v>
       </c>
       <c r="B55" t="n">
@@ -10106,7 +10258,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="n">
+      <c r="A56" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="B56" t="n">
@@ -10114,7 +10266,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="n">
+      <c r="A57" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="B57" t="n">

--- a/output/Data and Chart Outputs/china_nbs_clean_energy_products_monthly.xlsx
+++ b/output/Data and Chart Outputs/china_nbs_clean_energy_products_monthly.xlsx
@@ -169,7 +169,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>China power generation by source (NBS) (to Aug/26)</a:t>
+              <a:t>China power generation by source (NBS) (to Sep/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -199,12 +199,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$127</f>
+              <f>'Chart'!$A$2:$A$128</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$127</f>
+              <f>'Chart'!$B$2:$B$128</f>
             </numRef>
           </val>
         </ser>
@@ -227,12 +227,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$127</f>
+              <f>'Chart'!$A$2:$A$128</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$127</f>
+              <f>'Chart'!$C$2:$C$128</f>
             </numRef>
           </val>
         </ser>
@@ -255,12 +255,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$127</f>
+              <f>'Chart'!$A$2:$A$128</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$127</f>
+              <f>'Chart'!$D$2:$D$128</f>
             </numRef>
           </val>
         </ser>
@@ -283,12 +283,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$127</f>
+              <f>'Chart'!$A$2:$A$128</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$E$2:$E$127</f>
+              <f>'Chart'!$E$2:$E$128</f>
             </numRef>
           </val>
         </ser>
@@ -311,12 +311,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$127</f>
+              <f>'Chart'!$A$2:$A$128</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$F$2:$F$127</f>
+              <f>'Chart'!$F$2:$F$128</f>
             </numRef>
           </val>
         </ser>
@@ -417,7 +417,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>China fuel output y/y (NBS) (to Aug/26)</a:t>
+              <a:t>China fuel output y/y (NBS) (to Sep/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -453,12 +453,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - fuel output y-y'!$A$2:$A$131</f>
+              <f>'Chart - fuel output y-y'!$A$2:$A$132</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - fuel output y-y'!$B$2:$B$131</f>
+              <f>'Chart - fuel output y-y'!$B$2:$B$132</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -489,12 +489,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - fuel output y-y'!$A$2:$A$131</f>
+              <f>'Chart - fuel output y-y'!$A$2:$A$132</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - fuel output y-y'!$C$2:$C$131</f>
+              <f>'Chart - fuel output y-y'!$C$2:$C$132</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -525,12 +525,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - fuel output y-y'!$A$2:$A$131</f>
+              <f>'Chart - fuel output y-y'!$A$2:$A$132</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - fuel output y-y'!$D$2:$D$131</f>
+              <f>'Chart - fuel output y-y'!$D$2:$D$132</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -630,7 +630,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>China equipment output y/y (NBS) (to Aug/26)</a:t>
+              <a:t>China equipment output y/y (NBS) (to Sep/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -666,12 +666,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - equipment output y-y'!$A$2:$A$131</f>
+              <f>'Chart - equipment output y-y'!$A$2:$A$132</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - equipment output y-y'!$B$2:$B$131</f>
+              <f>'Chart - equipment output y-y'!$B$2:$B$132</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -702,12 +702,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - equipment output y-y'!$A$2:$A$131</f>
+              <f>'Chart - equipment output y-y'!$A$2:$A$132</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - equipment output y-y'!$C$2:$C$131</f>
+              <f>'Chart - equipment output y-y'!$C$2:$C$132</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -738,12 +738,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - equipment output y-y'!$A$2:$A$131</f>
+              <f>'Chart - equipment output y-y'!$A$2:$A$132</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - equipment output y-y'!$D$2:$D$131</f>
+              <f>'Chart - equipment output y-y'!$D$2:$D$132</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -774,12 +774,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - equipment output y-y'!$A$2:$A$131</f>
+              <f>'Chart - equipment output y-y'!$A$2:$A$132</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - equipment output y-y'!$E$2:$E$131</f>
+              <f>'Chart - equipment output y-y'!$E$2:$E$132</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -879,7 +879,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>China heavy industry output y/y (NBS) (to Aug/26)</a:t>
+              <a:t>China heavy industry output y/y (NBS) (to Sep/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -915,12 +915,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - heavy industry output y'!$A$2:$A$131</f>
+              <f>'Chart - heavy industry output y'!$A$2:$A$132</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - heavy industry output y'!$B$2:$B$131</f>
+              <f>'Chart - heavy industry output y'!$B$2:$B$132</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1016,7 +1016,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>China raw coal output (NBS) (to Aug/26)</a:t>
+              <a:t>China raw coal output (NBS) (to Sep/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1052,12 +1052,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - raw coal output'!$A$2:$A$116</f>
+              <f>'Chart - raw coal output'!$A$2:$A$117</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - raw coal output'!$B$2:$B$116</f>
+              <f>'Chart - raw coal output'!$B$2:$B$117</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1153,7 +1153,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>China coke output (NBS) (to Aug/26)</a:t>
+              <a:t>China coke output (NBS) (to Sep/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1189,12 +1189,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - coke output'!$A$2:$A$131</f>
+              <f>'Chart - coke output'!$A$2:$A$132</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - coke output'!$B$2:$B$131</f>
+              <f>'Chart - coke output'!$B$2:$B$132</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1290,7 +1290,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>China natural gas output (NBS) (to Aug/26)</a:t>
+              <a:t>China natural gas output (NBS) (to Sep/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1326,12 +1326,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - natural gas output'!$A$2:$A$127</f>
+              <f>'Chart - natural gas output'!$A$2:$A$128</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - natural gas output'!$B$2:$B$127</f>
+              <f>'Chart - natural gas output'!$B$2:$B$128</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1427,7 +1427,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>China electricity generation (total) (NBS) (to Aug/26)</a:t>
+              <a:t>China electricity generation (total) (NBS) (to Sep/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1463,12 +1463,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - electricity generation '!$A$2:$A$131</f>
+              <f>'Chart - electricity generation '!$A$2:$A$132</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - electricity generation '!$B$2:$B$131</f>
+              <f>'Chart - electricity generation '!$B$2:$B$132</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1564,7 +1564,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>China solar cell and power equipment output (NBS) (to Aug/26)</a:t>
+              <a:t>China solar cell and power equipment output (NBS) (to Sep/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1600,12 +1600,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - solar cell and power eq'!$A$2:$A$127</f>
+              <f>'Chart - solar cell and power eq'!$A$2:$A$128</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - solar cell and power eq'!$B$2:$B$127</f>
+              <f>'Chart - solar cell and power eq'!$B$2:$B$128</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1636,12 +1636,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - solar cell and power eq'!$A$2:$A$127</f>
+              <f>'Chart - solar cell and power eq'!$A$2:$A$128</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - solar cell and power eq'!$C$2:$C$127</f>
+              <f>'Chart - solar cell and power eq'!$C$2:$C$128</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1741,7 +1741,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>China vehicle output (NBS) (to Aug/26)</a:t>
+              <a:t>China vehicle output (NBS) (to Sep/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1777,12 +1777,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - vehicle output'!$A$2:$A$131</f>
+              <f>'Chart - vehicle output'!$A$2:$A$132</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - vehicle output'!$B$2:$B$131</f>
+              <f>'Chart - vehicle output'!$B$2:$B$132</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1813,12 +1813,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - vehicle output'!$A$2:$A$131</f>
+              <f>'Chart - vehicle output'!$A$2:$A$132</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - vehicle output'!$C$2:$C$131</f>
+              <f>'Chart - vehicle output'!$C$2:$C$132</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1918,7 +1918,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>China cement output (NBS) (to Aug/26)</a:t>
+              <a:t>China cement output (NBS) (to Sep/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1954,12 +1954,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - cement output'!$A$2:$A$131</f>
+              <f>'Chart - cement output'!$A$2:$A$132</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - cement output'!$B$2:$B$131</f>
+              <f>'Chart - cement output'!$B$2:$B$132</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2055,7 +2055,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>China power generation y/y by source (NBS) (to Aug/26)</a:t>
+              <a:t>China power generation y/y by source (NBS) (to Sep/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -2091,12 +2091,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - power generation y-y by'!$A$2:$A$131</f>
+              <f>'Chart - power generation y-y by'!$A$2:$A$132</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - power generation y-y by'!$B$2:$B$131</f>
+              <f>'Chart - power generation y-y by'!$B$2:$B$132</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2127,12 +2127,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - power generation y-y by'!$A$2:$A$131</f>
+              <f>'Chart - power generation y-y by'!$A$2:$A$132</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - power generation y-y by'!$C$2:$C$131</f>
+              <f>'Chart - power generation y-y by'!$C$2:$C$132</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2163,12 +2163,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - power generation y-y by'!$A$2:$A$131</f>
+              <f>'Chart - power generation y-y by'!$A$2:$A$132</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - power generation y-y by'!$D$2:$D$131</f>
+              <f>'Chart - power generation y-y by'!$D$2:$D$132</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2199,12 +2199,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - power generation y-y by'!$A$2:$A$131</f>
+              <f>'Chart - power generation y-y by'!$A$2:$A$132</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - power generation y-y by'!$E$2:$E$131</f>
+              <f>'Chart - power generation y-y by'!$E$2:$E$132</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2235,12 +2235,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - power generation y-y by'!$A$2:$A$131</f>
+              <f>'Chart - power generation y-y by'!$A$2:$A$132</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - power generation y-y by'!$F$2:$F$131</f>
+              <f>'Chart - power generation y-y by'!$F$2:$F$132</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2271,12 +2271,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - power generation y-y by'!$A$2:$A$131</f>
+              <f>'Chart - power generation y-y by'!$A$2:$A$132</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - power generation y-y by'!$G$2:$G$131</f>
+              <f>'Chart - power generation y-y by'!$G$2:$G$132</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -3089,7 +3089,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G131"/>
+  <dimension ref="A1:G132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -5853,6 +5853,29 @@
       </c>
       <c r="G131" t="n">
         <v>-0.8</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B132" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="C132" t="n">
+        <v>-18.1</v>
+      </c>
+      <c r="D132" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="E132" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="F132" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="G132" t="n">
+        <v>-1.2</v>
       </c>
     </row>
   </sheetData>
@@ -5867,7 +5890,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D131"/>
+  <dimension ref="A1:D132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -7656,6 +7679,20 @@
       </c>
       <c r="D131" t="n">
         <v>0.8</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B132" t="n">
+        <v>-6.8</v>
+      </c>
+      <c r="C132" t="n">
+        <v>-8.199999999999999</v>
+      </c>
+      <c r="D132" t="n">
+        <v>-1</v>
       </c>
     </row>
   </sheetData>
@@ -7670,7 +7707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E131"/>
+  <dimension ref="A1:E132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -9545,6 +9582,23 @@
       </c>
       <c r="E131" t="n">
         <v>21.9</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B132" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="C132" t="n">
+        <v>-7.2</v>
+      </c>
+      <c r="D132" t="n">
+        <v>-5.7</v>
+      </c>
+      <c r="E132" t="n">
+        <v>16.9</v>
       </c>
     </row>
   </sheetData>
@@ -9559,7 +9613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B131"/>
+  <dimension ref="A1:B132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -10615,6 +10669,14 @@
       </c>
       <c r="B131" t="n">
         <v>-11.7</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B132" t="n">
+        <v>-5.3</v>
       </c>
     </row>
   </sheetData>
@@ -10629,7 +10691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE131"/>
+  <dimension ref="A1:BE132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30647,6 +30709,179 @@
       </c>
       <c r="BE131" t="n">
         <v>-9</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="4" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B132" t="n">
+        <v>512.9</v>
+      </c>
+      <c r="C132" t="n">
+        <v>130.5</v>
+      </c>
+      <c r="D132" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="E132" t="n">
+        <v>77.59999999999999</v>
+      </c>
+      <c r="F132" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="G132" t="n">
+        <v>385.13</v>
+      </c>
+      <c r="H132" t="n">
+        <v>39.04</v>
+      </c>
+      <c r="I132" t="n">
+        <v>21</v>
+      </c>
+      <c r="J132" t="n">
+        <v>829.4</v>
+      </c>
+      <c r="K132" t="n">
+        <v>73.59</v>
+      </c>
+      <c r="L132" t="n">
+        <v>34.07</v>
+      </c>
+      <c r="M132" t="n">
+        <v>3063</v>
+      </c>
+      <c r="N132" t="n">
+        <v>1870</v>
+      </c>
+      <c r="O132" t="n">
+        <v>144.01</v>
+      </c>
+      <c r="P132" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>4734.3</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="S132" t="n">
+        <v>-18.1</v>
+      </c>
+      <c r="T132" t="n">
+        <v>1033.9</v>
+      </c>
+      <c r="U132" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="V132" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="W132" t="n">
+        <v>371.4</v>
+      </c>
+      <c r="X132" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>802.2</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>549.7</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>-6.8</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>3449.05</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>-8.199999999999999</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>373.16</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>196.7</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>7491.6</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>579.03</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>-13.5</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>-7.2</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>271.05</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>-5.7</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>23372</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>12457</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>12</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>-5.3</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>1131.19</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>-8.6</v>
       </c>
     </row>
   </sheetData>
@@ -33399,7 +33634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F127"/>
+  <dimension ref="A1:F128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -35748,6 +35983,26 @@
       </c>
       <c r="F127" t="n">
         <v>70</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B128" t="n">
+        <v>512.9</v>
+      </c>
+      <c r="C128" t="n">
+        <v>130.5</v>
+      </c>
+      <c r="D128" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="E128" t="n">
+        <v>77.59999999999999</v>
+      </c>
+      <c r="F128" t="n">
+        <v>64.40000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -35762,7 +36017,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B116"/>
+  <dimension ref="A1:B117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -36698,6 +36953,14 @@
       </c>
       <c r="B116" t="n">
         <v>361.82</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B117" t="n">
+        <v>385.13</v>
       </c>
     </row>
   </sheetData>
@@ -36712,7 +36975,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B131"/>
+  <dimension ref="A1:B132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -37768,6 +38031,14 @@
       </c>
       <c r="B131" t="n">
         <v>39.92</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B132" t="n">
+        <v>39.04</v>
       </c>
     </row>
   </sheetData>
@@ -37782,7 +38053,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B127"/>
+  <dimension ref="A1:B128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -38806,6 +39077,14 @@
       </c>
       <c r="B127" t="n">
         <v>21.4</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B128" t="n">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -38820,7 +39099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B131"/>
+  <dimension ref="A1:B132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -39876,6 +40155,14 @@
       </c>
       <c r="B131" t="n">
         <v>943.8</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B132" t="n">
+        <v>829.4</v>
       </c>
     </row>
   </sheetData>
@@ -39890,7 +40177,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C127"/>
+  <dimension ref="A1:C128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -41027,6 +41314,17 @@
       </c>
       <c r="C127" t="n">
         <v>28.06</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B128" t="n">
+        <v>73.59</v>
+      </c>
+      <c r="C128" t="n">
+        <v>34.07</v>
       </c>
     </row>
   </sheetData>
@@ -41041,7 +41339,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C131"/>
+  <dimension ref="A1:C132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -42420,6 +42718,17 @@
       </c>
       <c r="C131" t="n">
         <v>1647</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B132" t="n">
+        <v>3063</v>
+      </c>
+      <c r="C132" t="n">
+        <v>1870</v>
       </c>
     </row>
   </sheetData>
@@ -42434,7 +42743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B131"/>
+  <dimension ref="A1:B132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -43492,6 +43801,14 @@
         <v>129.08</v>
       </c>
     </row>
+    <row r="132">
+      <c r="A132" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B132" t="n">
+        <v>144.01</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
